--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,10 +549,11 @@
     <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
-    <t>2014: source value from OPERATING ROOM - NAME (131.7-.01)</t>
-  </si>
-  <si>
-    <t>Dim.OperatingRoom.OperatingRoomLocationIEN</t>
+    <t>2014: source value from OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - NAME (131.7-.01 &gt; 44-.01)</t>
+  </si>
+  <si>
+    <t>Dim.OperatingRoom.OperatingRoomLocationIEN
+Dim.Location.LocationName,Dim.Location.LocationName</t>
   </si>
   <si>
     <t>.name</t>
@@ -1657,7 +1658,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="105.8046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.7109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="53.3359375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="68.15625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -726,7 +726,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>2015: source value from OPERATING ROOM - TELEHONE (131.7-3)</t>
+    <t>2015: source value from OPERATING ROOM - TELEPHONE (131.7-3)</t>
   </si>
   <si>
     <t>Dim.OperatingRoom.Telephone</t>
@@ -1195,7 +1195,7 @@
     <t>For purposes of location, display and identification, knowing which locations are located within other locations is important.</t>
   </si>
   <si>
-    <t>2018: reference from OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - PRINCIPAL CLINC (131.7-.01 &gt; 44-1916)</t>
+    <t>2018: reference from OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - PRINCIPAL CLINIC (131.7-.01 &gt; 44-1916)</t>
   </si>
   <si>
     <t>Dim.OperatingRoom.OperatingRoomLocationIEN
@@ -1657,7 +1657,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="105.8046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="106.34375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="53.3359375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="68.15625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -496,7 +496,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFOperatingRoomStatus</t>
+    <t>http://va.gov/fhir/ValueSet/OperatingRoomStatus</t>
   </si>
   <si>
     <t>2017: terminologyMaps using VF_OperatingRoomStatus on OPERATING ROOM - INACTIVE? (131.7-99)</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file OPERATING ROOM (131.7) to us-core-location</t>
+    <t>This StructureDefinition contains the maps for VistA file OPERATING ROOM (131.7) to us-core-location.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="415">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1174,6 +1174,9 @@
   </si>
   <si>
     <t>Need to know who manages the location.</t>
+  </si>
+  <si>
+    <t>2192: target not supported</t>
   </si>
   <si>
     <t>.scopingEntity[classCode=ORG determinerKind=INSTANCE]</t>
@@ -7115,13 +7118,13 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7129,10 +7132,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7155,17 +7158,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7217,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7229,13 +7232,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7243,10 +7246,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7272,13 +7275,13 @@
         <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7328,7 +7331,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7349,7 +7352,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7357,10 +7360,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7469,10 +7472,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7583,10 +7586,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7699,10 +7702,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7728,10 +7731,10 @@
         <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7761,10 +7764,10 @@
         <v>153</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7782,7 +7785,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7803,7 +7806,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7811,10 +7814,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7837,13 +7840,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7894,7 +7897,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7915,7 +7918,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7923,10 +7926,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7949,13 +7952,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8006,7 +8009,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8027,7 +8030,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8035,10 +8038,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8061,13 +8064,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8118,7 +8121,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8139,7 +8142,7 @@
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8147,10 +8150,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8176,10 +8179,10 @@
         <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8230,7 +8233,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8259,10 +8262,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8285,17 +8288,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8344,7 +8347,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,7 +549,7 @@
     <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
   </si>
   <si>
-    <t>2014: source value from OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - NAME (131.7-.01 &gt; 44-.01)</t>
+    <t>2014: source value based on OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - NAME (131.7-.01 &gt; 44-.01)</t>
   </si>
   <si>
     <t>Dim.OperatingRoom.OperatingRoomLocationIEN
@@ -726,7 +726,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>2015: source value from OPERATING ROOM - TELEPHONE (131.7-3)</t>
+    <t>2015: source value based on OPERATING ROOM - TELEPHONE (131.7-3)</t>
   </si>
   <si>
     <t>Dim.OperatingRoom.Telephone</t>
@@ -1198,7 +1198,7 @@
     <t>For purposes of location, display and identification, knowing which locations are located within other locations is important.</t>
   </si>
   <si>
-    <t>2018: reference from OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - PRINCIPAL CLINIC (131.7-.01 &gt; 44-1916)</t>
+    <t>2018: reference based on OPERATING ROOM - NAME &gt; HOSPITAL LOCATION - PRINCIPAL CLINIC (131.7-.01 &gt; 44-1916)</t>
   </si>
   <si>
     <t>Dim.OperatingRoom.OperatingRoomLocationIEN
@@ -1660,7 +1660,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="106.34375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="110.4375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="53.3359375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="68.15625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -494,6 +494,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>see mapping [VF_OperatingRoomStatus](ConceptMap-VF-OperatingRoomStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/OperatingRoomStatus</t>
@@ -2991,9 +2994,11 @@
       <c r="X12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3026,24 +3031,24 @@
         <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3066,13 +3071,13 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3102,10 +3107,10 @@
         <v>110</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3123,7 +3128,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3144,18 +3149,18 @@
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3178,16 +3183,16 @@
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3237,7 +3242,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3252,13 +3257,13 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3266,10 +3271,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3292,19 +3297,19 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3353,7 +3358,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3374,7 +3379,7 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3382,10 +3387,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3408,17 +3413,17 @@
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3467,7 +3472,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3488,7 +3493,7 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3496,10 +3501,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3525,16 +3530,16 @@
         <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3562,10 +3567,10 @@
         <v>153</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3583,7 +3588,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3604,18 +3609,18 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3638,13 +3643,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3671,13 +3676,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Y18" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3695,7 +3700,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3716,18 +3721,18 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3750,13 +3755,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3807,7 +3812,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3828,7 +3833,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3836,10 +3841,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3862,13 +3867,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3919,7 +3924,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3940,7 +3945,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3948,10 +3953,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3980,7 +3985,7 @@
         <v>133</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>135</v>
@@ -4021,19 +4026,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4054,7 +4059,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4062,10 +4067,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4091,10 +4096,10 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4124,10 +4129,10 @@
         <v>153</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4145,7 +4150,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4154,7 +4159,7 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
@@ -4166,7 +4171,7 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4174,10 +4179,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4200,19 +4205,19 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4261,7 +4266,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4276,13 +4281,13 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4290,10 +4295,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4319,16 +4324,16 @@
         <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4356,10 +4361,10 @@
         <v>153</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4377,7 +4382,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4398,7 +4403,7 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4406,10 +4411,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4432,16 +4437,16 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4491,7 +4496,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4512,7 +4517,7 @@
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4520,10 +4525,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4546,13 +4551,13 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4603,7 +4608,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4624,7 +4629,7 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4632,10 +4637,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4658,19 +4663,19 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4719,7 +4724,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4734,13 +4739,13 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4748,10 +4753,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4774,13 +4779,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4831,7 +4836,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4852,7 +4857,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4860,10 +4865,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4892,7 +4897,7 @@
         <v>133</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>135</v>
@@ -4933,19 +4938,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4966,7 +4971,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4974,10 +4979,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5003,16 +5008,16 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5025,7 +5030,7 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -5040,10 +5045,10 @@
         <v>153</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5061,7 +5066,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5082,7 +5087,7 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5090,10 +5095,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5119,13 +5124,13 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5139,7 +5144,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5154,10 +5159,10 @@
         <v>153</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5175,7 +5180,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5196,7 +5201,7 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5204,10 +5209,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5230,19 +5235,19 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5255,7 +5260,7 @@
         <v>77</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>77</v>
@@ -5291,7 +5296,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5312,7 +5317,7 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5346,13 +5351,13 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5367,7 +5372,7 @@
         <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>77</v>
@@ -5403,7 +5408,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5424,7 +5429,7 @@
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5432,14 +5437,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5458,13 +5463,13 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5479,7 +5484,7 @@
         <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>77</v>
@@ -5515,7 +5520,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5536,7 +5541,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5544,14 +5549,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5570,16 +5575,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5593,7 +5598,7 @@
         <v>77</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>77</v>
@@ -5629,7 +5634,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5650,7 +5655,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5658,14 +5663,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5684,13 +5689,13 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5717,13 +5722,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5741,7 +5746,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5762,7 +5767,7 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5770,14 +5775,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5796,13 +5801,13 @@
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5817,7 +5822,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -5853,7 +5858,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5874,7 +5879,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5882,10 +5887,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5908,16 +5913,16 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5967,7 +5972,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5988,7 +5993,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5996,10 +6001,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6022,17 +6027,17 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6045,7 +6050,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6081,7 +6086,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6102,7 +6107,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6110,10 +6115,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6136,17 +6141,17 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6171,13 +6176,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6195,7 +6200,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6216,18 +6221,18 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6250,17 +6255,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6309,7 +6314,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6330,7 +6335,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6338,10 +6343,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6364,13 +6369,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6421,7 +6426,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6442,7 +6447,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6450,10 +6455,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6482,7 +6487,7 @@
         <v>133</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>135</v>
@@ -6535,7 +6540,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6556,7 +6561,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6564,14 +6569,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6593,10 +6598,10 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>135</v>
@@ -6651,7 +6656,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6680,10 +6685,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6706,13 +6711,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6763,7 +6768,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>86</v>
@@ -6784,7 +6789,7 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6792,10 +6797,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6818,13 +6823,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6875,7 +6880,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>86</v>
@@ -6896,7 +6901,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6904,10 +6909,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6930,13 +6935,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6987,7 +6992,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7008,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7016,10 +7021,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7042,19 +7047,19 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7103,7 +7108,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7118,13 +7123,13 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7132,10 +7137,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7158,17 +7163,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7217,7 +7222,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7232,13 +7237,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7246,10 +7251,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7272,16 +7277,16 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7331,7 +7336,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7352,7 +7357,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7360,10 +7365,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7386,13 +7391,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7443,7 +7448,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7464,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7472,10 +7477,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7504,7 +7509,7 @@
         <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7557,7 +7562,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7578,7 +7583,7 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7586,14 +7591,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7615,10 +7620,10 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>135</v>
@@ -7673,7 +7678,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7702,10 +7707,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7731,10 +7736,10 @@
         <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7764,10 +7769,10 @@
         <v>153</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7785,7 +7790,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7806,7 +7811,7 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7814,10 +7819,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7840,13 +7845,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7897,7 +7902,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7918,7 +7923,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7926,10 +7931,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7952,13 +7957,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8009,7 +8014,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8030,7 +8035,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8038,10 +8043,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8064,13 +8069,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8121,7 +8126,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8142,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8150,10 +8155,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8176,13 +8181,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8233,7 +8238,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8254,7 +8259,7 @@
         <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8262,10 +8267,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8288,17 +8293,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8347,7 +8352,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8368,7 +8373,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
+++ b/docs/StructureDefinition-ProcedureSurgeryLocationOR.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
